--- a/prueba-libros.xlsx
+++ b/prueba-libros.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PIERO\UC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\ubuntu\home\homeneocode\proyectos\libsau\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D93A925-72CC-46FB-BA2E-1294C6BAA8DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1699480A-E21E-4F65-A78F-3D256C266BED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3037" yWindow="3037" windowWidth="18851" windowHeight="9766" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Alfaguara" sheetId="1" r:id="rId1"/>
@@ -1159,7 +1159,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:CS107"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
